--- a/models/6365_SOTP_Model.xlsx
+++ b/models/6365_SOTP_Model.xlsx
@@ -718,7 +718,9 @@
           <t>DCF — Perpetuity Growth</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="9" t="n">
+        <v>7391</v>
+      </c>
       <c r="D13" s="10">
         <f>(C13-$C$12)/$C$12</f>
         <v/>
@@ -730,7 +732,9 @@
           <t>DCF — Exit Multiple</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n"/>
+      <c r="C14" s="9" t="n">
+        <v>8846</v>
+      </c>
       <c r="D14" s="10">
         <f>(C14-$C$12)/$C$12</f>
         <v/>
@@ -742,7 +746,9 @@
           <t>Comps — EV/EBITDA</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n"/>
+      <c r="C15" s="9" t="n">
+        <v>8200</v>
+      </c>
       <c r="D15" s="10">
         <f>(C15-$C$12)/$C$12</f>
         <v/>
@@ -754,7 +760,9 @@
           <t>Comps — PER</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n"/>
+      <c r="C16" s="9" t="n">
+        <v>7496</v>
+      </c>
       <c r="D16" s="10">
         <f>(C16-$C$12)/$C$12</f>
         <v/>

--- a/models/6365_SOTP_Model.xlsx
+++ b/models/6365_SOTP_Model.xlsx
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>7391</v>
+        <v>6709</v>
       </c>
       <c r="D13" s="10">
         <f>(C13-$C$12)/$C$12</f>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8846</v>
+        <v>10283</v>
       </c>
       <c r="D14" s="10">
         <f>(C14-$C$12)/$C$12</f>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>-4000</v>
+        <v>-6515</v>
       </c>
     </row>
     <row r="23">
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="C25" s="50" t="n">
-        <v>7000</v>
+        <v>4145</v>
       </c>
     </row>
     <row r="26">

--- a/models/6365_SOTP_Model.xlsx
+++ b/models/6365_SOTP_Model.xlsx
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>6709</v>
+        <v>5882</v>
       </c>
       <c r="D13" s="10">
         <f>(C13-$C$12)/$C$12</f>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>10283</v>
+        <v>9660</v>
       </c>
       <c r="D14" s="10">
         <f>(C14-$C$12)/$C$12</f>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>8200</v>
+        <v>9772</v>
       </c>
       <c r="D15" s="10">
         <f>(C15-$C$12)/$C$12</f>
